--- a/cheklist_and_test_cases/CL_&_TC_Graduate_work.xlsx
+++ b/cheklist_and_test_cases/CL_&_TC_Graduate_work.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+  <workbookPr filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
@@ -10,7 +10,7 @@
     <sheet name="Чек-лист" sheetId="1" r:id="rId1"/>
     <sheet name="Тест-кейсы" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="132">
   <si>
     <t>№</t>
   </si>
@@ -398,12 +398,30 @@
   </si>
   <si>
     <t>Поверка работы ссылок в хедере.</t>
+  </si>
+  <si>
+    <t>Выбор языка.</t>
+  </si>
+  <si>
+    <t>Выбор английского языка.</t>
+  </si>
+  <si>
+    <t>Нажать на кнопку "Язык".</t>
+  </si>
+  <si>
+    <t>Выбрать язык "English".</t>
+  </si>
+  <si>
+    <t>Проверить, что страница переведена на английский язык.</t>
+  </si>
+  <si>
+    <t>Страница сайта переведена на английский язык.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -956,9 +974,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -966,9 +981,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -984,6 +996,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -993,19 +1023,49 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1029,53 +1089,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1137,7 +1155,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -1172,7 +1190,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -1349,7 +1367,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1357,17 +1375,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="33.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="38"/>
+      <c r="B1" s="36"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -1376,10 +1394,10 @@
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
@@ -1388,10 +1406,10 @@
       <c r="B3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
@@ -1400,10 +1418,10 @@
       <c r="B4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
     </row>
     <row r="5" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
@@ -1412,87 +1430,99 @@
       <c r="B5" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-    </row>
-    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>4</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-    </row>
-    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+    </row>
+    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>5</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="33"/>
+        <v>3</v>
+      </c>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>6</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+    </row>
+    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>7</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
+        <v>15</v>
+      </c>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>8</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>9</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-    </row>
-    <row r="11" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="32">
-        <v>9</v>
-      </c>
-      <c r="B11" s="21" t="s">
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+    </row>
+    <row r="12" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="71">
+        <v>10</v>
+      </c>
+      <c r="B12" s="21" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="28"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="23"/>
+    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="28"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="22"/>
+      <c r="A14" s="23"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1519,55 +1549,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="66"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="61"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="63"/>
-      <c r="E2" s="61" t="s">
+      <c r="D2" s="58"/>
+      <c r="E2" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="67" t="s">
+      <c r="F2" s="62" t="s">
         <v>111</v>
       </c>
-      <c r="G2" s="67" t="s">
+      <c r="G2" s="62" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="58"/>
-      <c r="B3" s="59"/>
+      <c r="A3" s="54"/>
+      <c r="B3" s="56"/>
       <c r="C3" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="59"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
     </row>
     <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="50">
+      <c r="A4" s="64">
         <v>1</v>
       </c>
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="64" t="s">
         <v>110</v>
       </c>
       <c r="C4" s="16">
@@ -1576,268 +1606,268 @@
       <c r="D4" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="53" t="s">
+      <c r="E4" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="45" t="s">
+      <c r="F4" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="G4" s="45" t="s">
+      <c r="G4" s="40" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="51"/>
-      <c r="B5" s="51"/>
+      <c r="A5" s="65"/>
+      <c r="B5" s="65"/>
       <c r="C5" s="18">
         <v>2</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="54"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
     </row>
     <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="51"/>
-      <c r="B6" s="51"/>
+      <c r="A6" s="65"/>
+      <c r="B6" s="65"/>
       <c r="C6" s="18">
         <v>3</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="54"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
     </row>
     <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="51"/>
-      <c r="B7" s="51"/>
+      <c r="A7" s="65"/>
+      <c r="B7" s="65"/>
       <c r="C7" s="18">
         <v>4</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="54"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
     </row>
     <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="51"/>
-      <c r="B8" s="51"/>
+      <c r="A8" s="65"/>
+      <c r="B8" s="65"/>
       <c r="C8" s="18">
         <v>5</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="54"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="46"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
     </row>
     <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="51"/>
-      <c r="B9" s="51"/>
+      <c r="A9" s="65"/>
+      <c r="B9" s="65"/>
       <c r="C9" s="18">
         <v>6</v>
       </c>
       <c r="D9" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="54"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
     </row>
     <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="52"/>
-      <c r="B10" s="52"/>
+      <c r="A10" s="66"/>
+      <c r="B10" s="66"/>
       <c r="C10" s="18">
         <v>7</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="55"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
     </row>
     <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="52"/>
-      <c r="B11" s="52"/>
+      <c r="A11" s="66"/>
+      <c r="B11" s="66"/>
       <c r="C11" s="18">
         <v>8</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="E11" s="55"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
+      <c r="E11" s="69"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
     </row>
     <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="52"/>
-      <c r="B12" s="52"/>
+      <c r="A12" s="66"/>
+      <c r="B12" s="66"/>
       <c r="C12" s="18">
         <v>9</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="55"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
     </row>
     <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="52"/>
-      <c r="B13" s="52"/>
+      <c r="A13" s="66"/>
+      <c r="B13" s="66"/>
       <c r="C13" s="18">
         <v>10</v>
       </c>
       <c r="D13" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="55"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
     </row>
     <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="52"/>
-      <c r="B14" s="52"/>
+      <c r="A14" s="66"/>
+      <c r="B14" s="66"/>
       <c r="C14" s="18">
         <v>11</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="55"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
     </row>
     <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="52"/>
-      <c r="B15" s="52"/>
+      <c r="A15" s="66"/>
+      <c r="B15" s="66"/>
       <c r="C15" s="18">
         <v>12</v>
       </c>
       <c r="D15" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="55"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
     </row>
     <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="52"/>
-      <c r="B16" s="52"/>
+      <c r="A16" s="66"/>
+      <c r="B16" s="66"/>
       <c r="C16" s="18">
         <v>13</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="55"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="46"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
     </row>
     <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="52"/>
-      <c r="B17" s="52"/>
+      <c r="A17" s="66"/>
+      <c r="B17" s="66"/>
       <c r="C17" s="18">
         <v>14</v>
       </c>
       <c r="D17" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="55"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
     </row>
     <row r="18" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="52"/>
-      <c r="B18" s="52"/>
+      <c r="A18" s="66"/>
+      <c r="B18" s="66"/>
       <c r="C18" s="18">
         <v>15</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="55"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
+      <c r="E18" s="69"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
     </row>
     <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="52"/>
-      <c r="B19" s="52"/>
+      <c r="A19" s="66"/>
+      <c r="B19" s="66"/>
       <c r="C19" s="18">
         <v>16</v>
       </c>
       <c r="D19" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="E19" s="55"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
+      <c r="E19" s="69"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
     </row>
     <row r="20" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="52"/>
-      <c r="B20" s="52"/>
+      <c r="A20" s="66"/>
+      <c r="B20" s="66"/>
       <c r="C20" s="18">
         <v>17</v>
       </c>
       <c r="D20" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="55"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46"/>
+      <c r="E20" s="69"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
     </row>
     <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="52"/>
-      <c r="B21" s="52"/>
+      <c r="A21" s="66"/>
+      <c r="B21" s="66"/>
       <c r="C21" s="18">
         <v>18</v>
       </c>
       <c r="D21" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="55"/>
-      <c r="F21" s="46"/>
-      <c r="G21" s="46"/>
+      <c r="E21" s="69"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
     </row>
     <row r="22" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="52"/>
-      <c r="B22" s="52"/>
+      <c r="A22" s="66"/>
+      <c r="B22" s="66"/>
       <c r="C22" s="18">
         <v>19</v>
       </c>
       <c r="D22" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="E22" s="55"/>
-      <c r="F22" s="46"/>
-      <c r="G22" s="46"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
     </row>
     <row r="23" spans="1:7" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="52"/>
-      <c r="B23" s="52"/>
+      <c r="A23" s="66"/>
+      <c r="B23" s="66"/>
       <c r="C23" s="24">
         <v>20</v>
       </c>
       <c r="D23" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="E23" s="55"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="47"/>
+      <c r="E23" s="69"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
     </row>
     <row r="24" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="39">
+      <c r="A24" s="37">
         <v>2</v>
       </c>
-      <c r="B24" s="45" t="s">
+      <c r="B24" s="40" t="s">
         <v>120</v>
       </c>
       <c r="C24" s="16">
@@ -1846,47 +1876,47 @@
       <c r="D24" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="E24" s="45" t="s">
+      <c r="E24" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="F24" s="39" t="s">
+      <c r="F24" s="37" t="s">
         <v>113</v>
       </c>
-      <c r="G24" s="45" t="s">
+      <c r="G24" s="40" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="40"/>
-      <c r="B25" s="46"/>
+      <c r="A25" s="38"/>
+      <c r="B25" s="41"/>
       <c r="C25" s="18">
         <v>2</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="46"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="46"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="41"/>
     </row>
     <row r="26" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="40"/>
-      <c r="B26" s="46"/>
+      <c r="A26" s="38"/>
+      <c r="B26" s="41"/>
       <c r="C26" s="24">
         <v>3</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E26" s="46"/>
-      <c r="F26" s="41"/>
-      <c r="G26" s="47"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="42"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="39">
+      <c r="A27" s="37">
         <v>3</v>
       </c>
-      <c r="B27" s="42" t="s">
+      <c r="B27" s="46" t="s">
         <v>52</v>
       </c>
       <c r="C27" s="16">
@@ -1895,73 +1925,73 @@
       <c r="D27" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="E27" s="48" t="s">
+      <c r="E27" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="F27" s="39" t="s">
+      <c r="F27" s="37" t="s">
         <v>113</v>
       </c>
-      <c r="G27" s="39" t="s">
+      <c r="G27" s="37" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="40"/>
-      <c r="B28" s="43"/>
+      <c r="A28" s="38"/>
+      <c r="B28" s="47"/>
       <c r="C28" s="18">
         <v>2</v>
       </c>
       <c r="D28" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E28" s="57"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="40"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="38"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="40"/>
-      <c r="B29" s="43"/>
+      <c r="A29" s="38"/>
+      <c r="B29" s="47"/>
       <c r="C29" s="18">
         <v>3</v>
       </c>
       <c r="D29" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="E29" s="57"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="40"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
     </row>
     <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="40"/>
-      <c r="B30" s="43"/>
+      <c r="A30" s="38"/>
+      <c r="B30" s="47"/>
       <c r="C30" s="18">
         <v>4</v>
       </c>
       <c r="D30" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="E30" s="57"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="40"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="38"/>
+      <c r="G30" s="38"/>
     </row>
     <row r="31" spans="1:7" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="41"/>
-      <c r="B31" s="44"/>
+      <c r="A31" s="39"/>
+      <c r="B31" s="48"/>
       <c r="C31" s="20">
         <v>5</v>
       </c>
       <c r="D31" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="E31" s="49"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="41"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="39"/>
     </row>
     <row r="32" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="39">
+      <c r="A32" s="37">
         <v>4</v>
       </c>
-      <c r="B32" s="45" t="s">
+      <c r="B32" s="40" t="s">
         <v>121</v>
       </c>
       <c r="C32" s="16">
@@ -1970,34 +2000,34 @@
       <c r="D32" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E32" s="45" t="s">
+      <c r="E32" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="F32" s="39" t="s">
+      <c r="F32" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="G32" s="70" t="s">
+      <c r="G32" s="49" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="40"/>
-      <c r="B33" s="56"/>
+      <c r="A33" s="38"/>
+      <c r="B33" s="70"/>
       <c r="C33" s="20">
         <v>2</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E33" s="46"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="71"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="50"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="39">
+      <c r="A34" s="37">
         <v>5</v>
       </c>
-      <c r="B34" s="45" t="s">
+      <c r="B34" s="40" t="s">
         <v>122</v>
       </c>
       <c r="C34" s="16">
@@ -2006,34 +2036,34 @@
       <c r="D34" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E34" s="45" t="s">
+      <c r="E34" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="F34" s="69" t="s">
+      <c r="F34" s="51" t="s">
         <v>115</v>
       </c>
-      <c r="G34" s="39" t="s">
+      <c r="G34" s="37" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="41"/>
-      <c r="B35" s="56"/>
+      <c r="A35" s="39"/>
+      <c r="B35" s="70"/>
       <c r="C35" s="20">
         <v>2</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E35" s="47"/>
-      <c r="F35" s="72"/>
-      <c r="G35" s="41"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="39"/>
     </row>
     <row r="36" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="39">
+      <c r="A36" s="37">
         <v>6</v>
       </c>
-      <c r="B36" s="45" t="s">
+      <c r="B36" s="40" t="s">
         <v>123</v>
       </c>
       <c r="C36" s="16">
@@ -2042,34 +2072,34 @@
       <c r="D36" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E36" s="45" t="s">
+      <c r="E36" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="F36" s="39" t="s">
+      <c r="F36" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="G36" s="39" t="s">
+      <c r="G36" s="37" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="41"/>
-      <c r="B37" s="47"/>
+      <c r="A37" s="39"/>
+      <c r="B37" s="42"/>
       <c r="C37" s="20">
         <v>2</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="E37" s="47"/>
-      <c r="F37" s="41"/>
-      <c r="G37" s="41"/>
+      <c r="E37" s="42"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="39"/>
     </row>
     <row r="38" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="39">
+      <c r="A38" s="37">
         <v>7</v>
       </c>
-      <c r="B38" s="45" t="s">
+      <c r="B38" s="40" t="s">
         <v>124</v>
       </c>
       <c r="C38" s="16">
@@ -2078,34 +2108,34 @@
       <c r="D38" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="E38" s="45" t="s">
+      <c r="E38" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="F38" s="39" t="s">
+      <c r="F38" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="G38" s="39" t="s">
+      <c r="G38" s="37" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="41"/>
-      <c r="B39" s="47"/>
+      <c r="A39" s="39"/>
+      <c r="B39" s="42"/>
       <c r="C39" s="24">
         <v>2</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E39" s="47"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
+      <c r="E39" s="42"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="39"/>
     </row>
     <row r="40" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="39">
+      <c r="A40" s="37">
         <v>8</v>
       </c>
-      <c r="B40" s="45" t="s">
+      <c r="B40" s="40" t="s">
         <v>62</v>
       </c>
       <c r="C40" s="16">
@@ -2114,125 +2144,125 @@
       <c r="D40" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E40" s="48" t="s">
+      <c r="E40" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="F40" s="45" t="s">
+      <c r="F40" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="G40" s="39" t="s">
+      <c r="G40" s="37" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="40"/>
-      <c r="B41" s="46"/>
+      <c r="A41" s="38"/>
+      <c r="B41" s="41"/>
       <c r="C41" s="18">
         <v>2</v>
       </c>
       <c r="D41" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="E41" s="57"/>
-      <c r="F41" s="46"/>
-      <c r="G41" s="40"/>
+      <c r="E41" s="44"/>
+      <c r="F41" s="41"/>
+      <c r="G41" s="38"/>
     </row>
     <row r="42" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="40"/>
-      <c r="B42" s="46"/>
+      <c r="A42" s="38"/>
+      <c r="B42" s="41"/>
       <c r="C42" s="18">
         <v>3</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E42" s="57"/>
-      <c r="F42" s="46"/>
-      <c r="G42" s="40"/>
+      <c r="E42" s="44"/>
+      <c r="F42" s="41"/>
+      <c r="G42" s="38"/>
     </row>
     <row r="43" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A43" s="40"/>
-      <c r="B43" s="46"/>
+      <c r="A43" s="38"/>
+      <c r="B43" s="41"/>
       <c r="C43" s="18">
         <v>4</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E43" s="57"/>
-      <c r="F43" s="46"/>
-      <c r="G43" s="40"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="41"/>
+      <c r="G43" s="38"/>
     </row>
     <row r="44" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="40"/>
-      <c r="B44" s="46"/>
+      <c r="A44" s="38"/>
+      <c r="B44" s="41"/>
       <c r="C44" s="18">
         <v>5</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E44" s="57"/>
-      <c r="F44" s="46"/>
-      <c r="G44" s="40"/>
+      <c r="E44" s="44"/>
+      <c r="F44" s="41"/>
+      <c r="G44" s="38"/>
     </row>
     <row r="45" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="40"/>
-      <c r="B45" s="46"/>
+      <c r="A45" s="38"/>
+      <c r="B45" s="41"/>
       <c r="C45" s="18">
         <v>6</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E45" s="57"/>
-      <c r="F45" s="46"/>
-      <c r="G45" s="40"/>
+      <c r="E45" s="44"/>
+      <c r="F45" s="41"/>
+      <c r="G45" s="38"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="40"/>
-      <c r="B46" s="46"/>
+      <c r="A46" s="38"/>
+      <c r="B46" s="41"/>
       <c r="C46" s="18">
         <v>7</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E46" s="57"/>
-      <c r="F46" s="46"/>
-      <c r="G46" s="40"/>
+      <c r="E46" s="44"/>
+      <c r="F46" s="41"/>
+      <c r="G46" s="38"/>
     </row>
     <row r="47" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="40"/>
-      <c r="B47" s="46"/>
+      <c r="A47" s="38"/>
+      <c r="B47" s="41"/>
       <c r="C47" s="18">
         <v>8</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E47" s="57"/>
-      <c r="F47" s="46"/>
-      <c r="G47" s="40"/>
+      <c r="E47" s="44"/>
+      <c r="F47" s="41"/>
+      <c r="G47" s="38"/>
     </row>
     <row r="48" spans="1:7" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="41"/>
-      <c r="B48" s="47"/>
+      <c r="A48" s="39"/>
+      <c r="B48" s="42"/>
       <c r="C48" s="24">
         <v>9</v>
       </c>
       <c r="D48" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E48" s="49"/>
-      <c r="F48" s="47"/>
-      <c r="G48" s="41"/>
+      <c r="E48" s="45"/>
+      <c r="F48" s="42"/>
+      <c r="G48" s="39"/>
     </row>
     <row r="49" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A49" s="39">
+      <c r="A49" s="37">
         <v>9</v>
       </c>
-      <c r="B49" s="42" t="s">
+      <c r="B49" s="46" t="s">
         <v>69</v>
       </c>
       <c r="C49" s="16">
@@ -2241,138 +2271,138 @@
       <c r="D49" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E49" s="45" t="s">
+      <c r="E49" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="F49" s="45" t="s">
+      <c r="F49" s="40" t="s">
         <v>115</v>
       </c>
-      <c r="G49" s="39" t="s">
+      <c r="G49" s="37" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="40"/>
-      <c r="B50" s="43"/>
+      <c r="A50" s="38"/>
+      <c r="B50" s="47"/>
       <c r="C50" s="18">
         <v>2</v>
       </c>
       <c r="D50" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="E50" s="46"/>
-      <c r="F50" s="46"/>
-      <c r="G50" s="40"/>
+      <c r="E50" s="41"/>
+      <c r="F50" s="41"/>
+      <c r="G50" s="38"/>
     </row>
     <row r="51" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="40"/>
-      <c r="B51" s="43"/>
+      <c r="A51" s="38"/>
+      <c r="B51" s="47"/>
       <c r="C51" s="18">
         <v>3</v>
       </c>
-      <c r="D51" s="34" t="s">
+      <c r="D51" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="E51" s="46"/>
-      <c r="F51" s="46"/>
-      <c r="G51" s="40"/>
+      <c r="E51" s="41"/>
+      <c r="F51" s="41"/>
+      <c r="G51" s="38"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="40"/>
-      <c r="B52" s="43"/>
+      <c r="A52" s="38"/>
+      <c r="B52" s="47"/>
       <c r="C52" s="18">
         <v>4</v>
       </c>
-      <c r="D52" s="34" t="s">
+      <c r="D52" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="E52" s="46"/>
-      <c r="F52" s="46"/>
-      <c r="G52" s="40"/>
+      <c r="E52" s="41"/>
+      <c r="F52" s="41"/>
+      <c r="G52" s="38"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="40"/>
-      <c r="B53" s="43"/>
+      <c r="A53" s="38"/>
+      <c r="B53" s="47"/>
       <c r="C53" s="18">
         <v>5</v>
       </c>
-      <c r="D53" s="34" t="s">
+      <c r="D53" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="E53" s="46"/>
-      <c r="F53" s="46"/>
-      <c r="G53" s="40"/>
+      <c r="E53" s="41"/>
+      <c r="F53" s="41"/>
+      <c r="G53" s="38"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="40"/>
-      <c r="B54" s="43"/>
+      <c r="A54" s="38"/>
+      <c r="B54" s="47"/>
       <c r="C54" s="18">
         <v>6</v>
       </c>
-      <c r="D54" s="34" t="s">
+      <c r="D54" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="E54" s="46"/>
-      <c r="F54" s="46"/>
-      <c r="G54" s="40"/>
+      <c r="E54" s="41"/>
+      <c r="F54" s="41"/>
+      <c r="G54" s="38"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="40"/>
-      <c r="B55" s="43"/>
+      <c r="A55" s="38"/>
+      <c r="B55" s="47"/>
       <c r="C55" s="18">
         <v>7</v>
       </c>
-      <c r="D55" s="34" t="s">
+      <c r="D55" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="E55" s="46"/>
-      <c r="F55" s="46"/>
-      <c r="G55" s="40"/>
+      <c r="E55" s="41"/>
+      <c r="F55" s="41"/>
+      <c r="G55" s="38"/>
     </row>
     <row r="56" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A56" s="40"/>
-      <c r="B56" s="43"/>
+      <c r="A56" s="38"/>
+      <c r="B56" s="47"/>
       <c r="C56" s="18">
         <v>8</v>
       </c>
-      <c r="D56" s="34" t="s">
+      <c r="D56" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="E56" s="46"/>
-      <c r="F56" s="46"/>
-      <c r="G56" s="40"/>
+      <c r="E56" s="41"/>
+      <c r="F56" s="41"/>
+      <c r="G56" s="38"/>
     </row>
     <row r="57" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A57" s="40"/>
-      <c r="B57" s="43"/>
+      <c r="A57" s="38"/>
+      <c r="B57" s="47"/>
       <c r="C57" s="18">
         <v>9</v>
       </c>
-      <c r="D57" s="34" t="s">
+      <c r="D57" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="E57" s="46"/>
-      <c r="F57" s="46"/>
-      <c r="G57" s="40"/>
+      <c r="E57" s="41"/>
+      <c r="F57" s="41"/>
+      <c r="G57" s="38"/>
     </row>
     <row r="58" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="41"/>
-      <c r="B58" s="44"/>
+      <c r="A58" s="39"/>
+      <c r="B58" s="48"/>
       <c r="C58" s="24">
         <v>10</v>
       </c>
-      <c r="D58" s="35" t="s">
+      <c r="D58" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="E58" s="46"/>
-      <c r="F58" s="47"/>
-      <c r="G58" s="41"/>
+      <c r="E58" s="41"/>
+      <c r="F58" s="42"/>
+      <c r="G58" s="39"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="39">
+      <c r="A59" s="37">
         <v>10</v>
       </c>
-      <c r="B59" s="42" t="s">
+      <c r="B59" s="46" t="s">
         <v>125</v>
       </c>
       <c r="C59" s="16">
@@ -2381,200 +2411,200 @@
       <c r="D59" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="E59" s="45" t="s">
+      <c r="E59" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="F59" s="39" t="s">
+      <c r="F59" s="37" t="s">
         <v>113</v>
       </c>
-      <c r="G59" s="39" t="s">
+      <c r="G59" s="37" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="40"/>
-      <c r="B60" s="43"/>
+      <c r="A60" s="38"/>
+      <c r="B60" s="47"/>
       <c r="C60" s="18">
         <v>2</v>
       </c>
-      <c r="D60" s="34" t="s">
+      <c r="D60" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="E60" s="47"/>
-      <c r="F60" s="40"/>
-      <c r="G60" s="40"/>
+      <c r="E60" s="42"/>
+      <c r="F60" s="38"/>
+      <c r="G60" s="38"/>
     </row>
     <row r="61" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="40"/>
-      <c r="B61" s="43"/>
+      <c r="A61" s="38"/>
+      <c r="B61" s="47"/>
       <c r="C61" s="18">
         <v>3</v>
       </c>
-      <c r="D61" s="34" t="s">
+      <c r="D61" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="E61" s="48" t="s">
+      <c r="E61" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="F61" s="40"/>
-      <c r="G61" s="40"/>
+      <c r="F61" s="38"/>
+      <c r="G61" s="38"/>
     </row>
     <row r="62" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="40"/>
-      <c r="B62" s="43"/>
+      <c r="A62" s="38"/>
+      <c r="B62" s="47"/>
       <c r="C62" s="18">
         <v>4</v>
       </c>
-      <c r="D62" s="34" t="s">
+      <c r="D62" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="E62" s="57"/>
-      <c r="F62" s="40"/>
-      <c r="G62" s="40"/>
+      <c r="E62" s="44"/>
+      <c r="F62" s="38"/>
+      <c r="G62" s="38"/>
     </row>
     <row r="63" spans="1:7" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="40"/>
-      <c r="B63" s="43"/>
+      <c r="A63" s="38"/>
+      <c r="B63" s="47"/>
       <c r="C63" s="18">
         <v>5</v>
       </c>
-      <c r="D63" s="34" t="s">
+      <c r="D63" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="E63" s="49"/>
-      <c r="F63" s="40"/>
-      <c r="G63" s="40"/>
+      <c r="E63" s="45"/>
+      <c r="F63" s="38"/>
+      <c r="G63" s="38"/>
     </row>
     <row r="64" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="40"/>
-      <c r="B64" s="43"/>
+      <c r="A64" s="38"/>
+      <c r="B64" s="47"/>
       <c r="C64" s="18">
         <v>6</v>
       </c>
-      <c r="D64" s="34" t="s">
+      <c r="D64" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="E64" s="48" t="s">
+      <c r="E64" s="43" t="s">
         <v>102</v>
       </c>
-      <c r="F64" s="40"/>
-      <c r="G64" s="40"/>
+      <c r="F64" s="38"/>
+      <c r="G64" s="38"/>
     </row>
     <row r="65" spans="1:7" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="40"/>
-      <c r="B65" s="43"/>
+      <c r="A65" s="38"/>
+      <c r="B65" s="47"/>
       <c r="C65" s="18">
         <v>7</v>
       </c>
-      <c r="D65" s="34" t="s">
+      <c r="D65" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="E65" s="49"/>
-      <c r="F65" s="40"/>
-      <c r="G65" s="40"/>
+      <c r="E65" s="45"/>
+      <c r="F65" s="38"/>
+      <c r="G65" s="38"/>
     </row>
     <row r="66" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="40"/>
-      <c r="B66" s="43"/>
+      <c r="A66" s="38"/>
+      <c r="B66" s="47"/>
       <c r="C66" s="18">
         <v>8</v>
       </c>
-      <c r="D66" s="34" t="s">
+      <c r="D66" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="E66" s="48" t="s">
+      <c r="E66" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="F66" s="40"/>
-      <c r="G66" s="40"/>
+      <c r="F66" s="38"/>
+      <c r="G66" s="38"/>
     </row>
     <row r="67" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="40"/>
-      <c r="B67" s="43"/>
+      <c r="A67" s="38"/>
+      <c r="B67" s="47"/>
       <c r="C67" s="18">
         <v>9</v>
       </c>
-      <c r="D67" s="34" t="s">
+      <c r="D67" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="E67" s="49"/>
-      <c r="F67" s="40"/>
-      <c r="G67" s="40"/>
+      <c r="E67" s="45"/>
+      <c r="F67" s="38"/>
+      <c r="G67" s="38"/>
     </row>
     <row r="68" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="40"/>
-      <c r="B68" s="43"/>
+      <c r="A68" s="38"/>
+      <c r="B68" s="47"/>
       <c r="C68" s="18">
         <v>10</v>
       </c>
-      <c r="D68" s="34" t="s">
+      <c r="D68" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="E68" s="45" t="s">
+      <c r="E68" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="F68" s="40"/>
-      <c r="G68" s="40"/>
+      <c r="F68" s="38"/>
+      <c r="G68" s="38"/>
     </row>
     <row r="69" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="40"/>
-      <c r="B69" s="43"/>
+      <c r="A69" s="38"/>
+      <c r="B69" s="47"/>
       <c r="C69" s="18">
         <v>11</v>
       </c>
-      <c r="D69" s="34" t="s">
+      <c r="D69" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="E69" s="46"/>
-      <c r="F69" s="40"/>
-      <c r="G69" s="40"/>
+      <c r="E69" s="41"/>
+      <c r="F69" s="38"/>
+      <c r="G69" s="38"/>
     </row>
     <row r="70" spans="1:7" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="40"/>
-      <c r="B70" s="43"/>
+      <c r="A70" s="38"/>
+      <c r="B70" s="47"/>
       <c r="C70" s="18">
         <v>12</v>
       </c>
-      <c r="D70" s="34" t="s">
+      <c r="D70" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="E70" s="47"/>
-      <c r="F70" s="40"/>
-      <c r="G70" s="40"/>
+      <c r="E70" s="42"/>
+      <c r="F70" s="38"/>
+      <c r="G70" s="38"/>
     </row>
     <row r="71" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="40"/>
-      <c r="B71" s="43"/>
+      <c r="A71" s="38"/>
+      <c r="B71" s="47"/>
       <c r="C71" s="18">
         <v>13</v>
       </c>
-      <c r="D71" s="34" t="s">
+      <c r="D71" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="E71" s="48" t="s">
+      <c r="E71" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="F71" s="40"/>
-      <c r="G71" s="40"/>
+      <c r="F71" s="38"/>
+      <c r="G71" s="38"/>
     </row>
     <row r="72" spans="1:7" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="41"/>
-      <c r="B72" s="44"/>
+      <c r="A72" s="39"/>
+      <c r="B72" s="48"/>
       <c r="C72" s="24">
         <v>14</v>
       </c>
-      <c r="D72" s="35" t="s">
+      <c r="D72" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="E72" s="49"/>
-      <c r="F72" s="41"/>
-      <c r="G72" s="41"/>
+      <c r="E72" s="45"/>
+      <c r="F72" s="39"/>
+      <c r="G72" s="39"/>
     </row>
     <row r="73" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="39">
+      <c r="A73" s="37">
         <v>11</v>
       </c>
-      <c r="B73" s="42" t="s">
+      <c r="B73" s="46" t="s">
         <v>15</v>
       </c>
       <c r="C73" s="16">
@@ -2583,457 +2613,517 @@
       <c r="D73" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="E73" s="48" t="s">
+      <c r="E73" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="F73" s="45" t="s">
+      <c r="F73" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="G73" s="45" t="s">
+      <c r="G73" s="40" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="40"/>
-      <c r="B74" s="43"/>
+      <c r="A74" s="38"/>
+      <c r="B74" s="47"/>
       <c r="C74" s="18">
         <v>2</v>
       </c>
-      <c r="D74" s="34" t="s">
+      <c r="D74" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="E74" s="57"/>
-      <c r="F74" s="46"/>
-      <c r="G74" s="46"/>
+      <c r="E74" s="44"/>
+      <c r="F74" s="41"/>
+      <c r="G74" s="41"/>
     </row>
     <row r="75" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A75" s="40"/>
-      <c r="B75" s="43"/>
+      <c r="A75" s="38"/>
+      <c r="B75" s="47"/>
       <c r="C75" s="18">
         <v>3</v>
       </c>
-      <c r="D75" s="34" t="s">
+      <c r="D75" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="E75" s="57"/>
-      <c r="F75" s="46"/>
-      <c r="G75" s="46"/>
+      <c r="E75" s="44"/>
+      <c r="F75" s="41"/>
+      <c r="G75" s="41"/>
     </row>
     <row r="76" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="40"/>
-      <c r="B76" s="43"/>
+      <c r="A76" s="38"/>
+      <c r="B76" s="47"/>
       <c r="C76" s="18">
         <v>4</v>
       </c>
-      <c r="D76" s="34" t="s">
+      <c r="D76" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="E76" s="49"/>
-      <c r="F76" s="46"/>
-      <c r="G76" s="46"/>
+      <c r="E76" s="45"/>
+      <c r="F76" s="41"/>
+      <c r="G76" s="41"/>
     </row>
     <row r="77" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="40"/>
-      <c r="B77" s="43"/>
+      <c r="A77" s="38"/>
+      <c r="B77" s="47"/>
       <c r="C77" s="18">
         <v>5</v>
       </c>
-      <c r="D77" s="34" t="s">
+      <c r="D77" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="E77" s="48" t="s">
+      <c r="E77" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="F77" s="46"/>
-      <c r="G77" s="46"/>
+      <c r="F77" s="41"/>
+      <c r="G77" s="41"/>
     </row>
     <row r="78" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="40"/>
-      <c r="B78" s="43"/>
+      <c r="A78" s="38"/>
+      <c r="B78" s="47"/>
       <c r="C78" s="18">
         <v>6</v>
       </c>
-      <c r="D78" s="34" t="s">
+      <c r="D78" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="E78" s="57"/>
-      <c r="F78" s="46"/>
-      <c r="G78" s="46"/>
+      <c r="E78" s="44"/>
+      <c r="F78" s="41"/>
+      <c r="G78" s="41"/>
     </row>
     <row r="79" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A79" s="40"/>
-      <c r="B79" s="43"/>
+      <c r="A79" s="38"/>
+      <c r="B79" s="47"/>
       <c r="C79" s="18">
         <v>7</v>
       </c>
-      <c r="D79" s="34" t="s">
+      <c r="D79" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="E79" s="57"/>
-      <c r="F79" s="46"/>
-      <c r="G79" s="46"/>
+      <c r="E79" s="44"/>
+      <c r="F79" s="41"/>
+      <c r="G79" s="41"/>
     </row>
     <row r="80" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="40"/>
-      <c r="B80" s="43"/>
+      <c r="A80" s="38"/>
+      <c r="B80" s="47"/>
       <c r="C80" s="18">
         <v>8</v>
       </c>
-      <c r="D80" s="34" t="s">
+      <c r="D80" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="E80" s="49"/>
-      <c r="F80" s="46"/>
-      <c r="G80" s="46"/>
+      <c r="E80" s="45"/>
+      <c r="F80" s="41"/>
+      <c r="G80" s="41"/>
     </row>
     <row r="81" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="40"/>
-      <c r="B81" s="43"/>
+      <c r="A81" s="38"/>
+      <c r="B81" s="47"/>
       <c r="C81" s="18">
         <v>9</v>
       </c>
-      <c r="D81" s="34" t="s">
+      <c r="D81" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="E81" s="48" t="s">
+      <c r="E81" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="F81" s="46"/>
-      <c r="G81" s="46"/>
+      <c r="F81" s="41"/>
+      <c r="G81" s="41"/>
     </row>
     <row r="82" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="40"/>
-      <c r="B82" s="43"/>
+      <c r="A82" s="38"/>
+      <c r="B82" s="47"/>
       <c r="C82" s="18">
         <v>10</v>
       </c>
-      <c r="D82" s="34" t="s">
+      <c r="D82" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="E82" s="57"/>
-      <c r="F82" s="46"/>
-      <c r="G82" s="46"/>
+      <c r="E82" s="44"/>
+      <c r="F82" s="41"/>
+      <c r="G82" s="41"/>
     </row>
     <row r="83" spans="1:7" ht="90" x14ac:dyDescent="0.25">
-      <c r="A83" s="40"/>
-      <c r="B83" s="43"/>
+      <c r="A83" s="38"/>
+      <c r="B83" s="47"/>
       <c r="C83" s="18">
         <v>11</v>
       </c>
-      <c r="D83" s="34" t="s">
+      <c r="D83" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="E83" s="57"/>
-      <c r="F83" s="46"/>
-      <c r="G83" s="46"/>
+      <c r="E83" s="44"/>
+      <c r="F83" s="41"/>
+      <c r="G83" s="41"/>
     </row>
     <row r="84" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="40"/>
-      <c r="B84" s="43"/>
+      <c r="A84" s="38"/>
+      <c r="B84" s="47"/>
       <c r="C84" s="18">
         <v>12</v>
       </c>
-      <c r="D84" s="34" t="s">
+      <c r="D84" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="E84" s="49"/>
-      <c r="F84" s="46"/>
-      <c r="G84" s="46"/>
+      <c r="E84" s="45"/>
+      <c r="F84" s="41"/>
+      <c r="G84" s="41"/>
     </row>
     <row r="85" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="40"/>
-      <c r="B85" s="43"/>
+      <c r="A85" s="38"/>
+      <c r="B85" s="47"/>
       <c r="C85" s="18">
         <v>13</v>
       </c>
-      <c r="D85" s="34" t="s">
+      <c r="D85" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="E85" s="48" t="s">
+      <c r="E85" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="F85" s="46"/>
-      <c r="G85" s="46"/>
+      <c r="F85" s="41"/>
+      <c r="G85" s="41"/>
     </row>
     <row r="86" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="40"/>
-      <c r="B86" s="43"/>
+      <c r="A86" s="38"/>
+      <c r="B86" s="47"/>
       <c r="C86" s="18">
         <v>14</v>
       </c>
-      <c r="D86" s="34" t="s">
+      <c r="D86" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="E86" s="57"/>
-      <c r="F86" s="46"/>
-      <c r="G86" s="46"/>
+      <c r="E86" s="44"/>
+      <c r="F86" s="41"/>
+      <c r="G86" s="41"/>
     </row>
     <row r="87" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A87" s="40"/>
-      <c r="B87" s="43"/>
+      <c r="A87" s="38"/>
+      <c r="B87" s="47"/>
       <c r="C87" s="18">
         <v>15</v>
       </c>
-      <c r="D87" s="34" t="s">
+      <c r="D87" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="E87" s="57"/>
-      <c r="F87" s="46"/>
-      <c r="G87" s="46"/>
+      <c r="E87" s="44"/>
+      <c r="F87" s="41"/>
+      <c r="G87" s="41"/>
     </row>
     <row r="88" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="40"/>
-      <c r="B88" s="43"/>
+      <c r="A88" s="38"/>
+      <c r="B88" s="47"/>
       <c r="C88" s="18">
         <v>16</v>
       </c>
-      <c r="D88" s="34" t="s">
+      <c r="D88" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="E88" s="49"/>
-      <c r="F88" s="46"/>
-      <c r="G88" s="46"/>
+      <c r="E88" s="45"/>
+      <c r="F88" s="41"/>
+      <c r="G88" s="41"/>
     </row>
     <row r="89" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="40"/>
-      <c r="B89" s="43"/>
+      <c r="A89" s="38"/>
+      <c r="B89" s="47"/>
       <c r="C89" s="18">
         <v>17</v>
       </c>
-      <c r="D89" s="34" t="s">
+      <c r="D89" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="E89" s="48" t="s">
+      <c r="E89" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="F89" s="46"/>
-      <c r="G89" s="46"/>
+      <c r="F89" s="41"/>
+      <c r="G89" s="41"/>
     </row>
     <row r="90" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A90" s="40"/>
-      <c r="B90" s="43"/>
+      <c r="A90" s="38"/>
+      <c r="B90" s="47"/>
       <c r="C90" s="18">
         <v>18</v>
       </c>
-      <c r="D90" s="34" t="s">
+      <c r="D90" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="E90" s="57"/>
-      <c r="F90" s="46"/>
-      <c r="G90" s="46"/>
+      <c r="E90" s="44"/>
+      <c r="F90" s="41"/>
+      <c r="G90" s="41"/>
     </row>
     <row r="91" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="40"/>
-      <c r="B91" s="43"/>
+      <c r="A91" s="38"/>
+      <c r="B91" s="47"/>
       <c r="C91" s="18">
         <v>19</v>
       </c>
-      <c r="D91" s="34" t="s">
+      <c r="D91" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="E91" s="57"/>
-      <c r="F91" s="46"/>
-      <c r="G91" s="46"/>
+      <c r="E91" s="44"/>
+      <c r="F91" s="41"/>
+      <c r="G91" s="41"/>
     </row>
     <row r="92" spans="1:7" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="40"/>
-      <c r="B92" s="43"/>
+      <c r="A92" s="38"/>
+      <c r="B92" s="47"/>
       <c r="C92" s="18">
         <v>20</v>
       </c>
-      <c r="D92" s="34" t="s">
+      <c r="D92" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="E92" s="49"/>
-      <c r="F92" s="46"/>
-      <c r="G92" s="46"/>
+      <c r="E92" s="45"/>
+      <c r="F92" s="41"/>
+      <c r="G92" s="41"/>
     </row>
     <row r="93" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="40"/>
-      <c r="B93" s="43"/>
+      <c r="A93" s="38"/>
+      <c r="B93" s="47"/>
       <c r="C93" s="18">
         <v>21</v>
       </c>
-      <c r="D93" s="34" t="s">
+      <c r="D93" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="E93" s="48" t="s">
+      <c r="E93" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="F93" s="46"/>
-      <c r="G93" s="46"/>
+      <c r="F93" s="41"/>
+      <c r="G93" s="41"/>
     </row>
     <row r="94" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A94" s="40"/>
-      <c r="B94" s="43"/>
+      <c r="A94" s="38"/>
+      <c r="B94" s="47"/>
       <c r="C94" s="18">
         <v>22</v>
       </c>
-      <c r="D94" s="34" t="s">
+      <c r="D94" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="E94" s="57"/>
-      <c r="F94" s="46"/>
-      <c r="G94" s="46"/>
+      <c r="E94" s="44"/>
+      <c r="F94" s="41"/>
+      <c r="G94" s="41"/>
     </row>
     <row r="95" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="41"/>
-      <c r="B95" s="44"/>
-      <c r="C95" s="20">
+      <c r="A95" s="39"/>
+      <c r="B95" s="48"/>
+      <c r="C95" s="24">
         <v>23</v>
       </c>
-      <c r="D95" s="36" t="s">
+      <c r="D95" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="E95" s="49"/>
-      <c r="F95" s="47"/>
-      <c r="G95" s="47"/>
+      <c r="E95" s="45"/>
+      <c r="F95" s="42"/>
+      <c r="G95" s="42"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F96" s="13"/>
-    </row>
-    <row r="97" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F97" s="13"/>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F98" s="13"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F99" s="13"/>
-    </row>
-    <row r="100" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F100" s="13"/>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F101" s="13"/>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F102" s="13"/>
-    </row>
-    <row r="103" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F103" s="13"/>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="40">
+        <v>12</v>
+      </c>
+      <c r="B96" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="C96" s="16">
+        <v>1</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E96" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="F96" s="40" t="s">
+        <v>113</v>
+      </c>
+      <c r="G96" s="40" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="41"/>
+      <c r="B97" s="47"/>
+      <c r="C97" s="18">
+        <v>2</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E97" s="41"/>
+      <c r="F97" s="41"/>
+      <c r="G97" s="41"/>
+    </row>
+    <row r="98" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="42"/>
+      <c r="B98" s="48"/>
+      <c r="C98" s="20">
+        <v>3</v>
+      </c>
+      <c r="D98" s="72" t="s">
+        <v>130</v>
+      </c>
+      <c r="E98" s="42"/>
+      <c r="F98" s="42"/>
+      <c r="G98" s="42"/>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F99" s="15"/>
+      <c r="G99" s="15"/>
+    </row>
+    <row r="100" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F100" s="15"/>
+      <c r="G100" s="15"/>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F101" s="15"/>
+      <c r="G101" s="15"/>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F102" s="15"/>
+      <c r="G102" s="15"/>
+    </row>
+    <row r="103" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F103" s="15"/>
+      <c r="G103" s="15"/>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="29"/>
       <c r="B104" s="15"/>
       <c r="C104" s="30"/>
       <c r="D104" s="8"/>
       <c r="E104" s="15"/>
-      <c r="F104" s="13"/>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F104" s="15"/>
+      <c r="G104" s="15"/>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="29"/>
       <c r="B105" s="15"/>
       <c r="C105" s="30"/>
       <c r="D105" s="8"/>
       <c r="E105" s="15"/>
-      <c r="F105" s="13"/>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F105" s="15"/>
+      <c r="G105" s="15"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="29"/>
       <c r="B106" s="15"/>
       <c r="C106" s="30"/>
       <c r="D106" s="8"/>
       <c r="E106" s="15"/>
-      <c r="F106" s="13"/>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F106" s="15"/>
+      <c r="G106" s="15"/>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="29"/>
       <c r="B107" s="15"/>
       <c r="C107" s="30"/>
       <c r="D107" s="8"/>
       <c r="E107" s="15"/>
-      <c r="F107" s="13"/>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F107" s="15"/>
+      <c r="G107" s="15"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="29"/>
       <c r="B108" s="15"/>
       <c r="C108" s="30"/>
       <c r="D108" s="31"/>
       <c r="E108" s="15"/>
-      <c r="F108" s="13"/>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F108" s="15"/>
+      <c r="G108" s="15"/>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="29"/>
       <c r="B109" s="15"/>
       <c r="C109" s="30"/>
       <c r="D109" s="31"/>
       <c r="E109" s="15"/>
-      <c r="F109" s="13"/>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F109" s="15"/>
+      <c r="G109" s="15"/>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="29"/>
       <c r="B110" s="15"/>
       <c r="C110" s="30"/>
       <c r="D110" s="8"/>
       <c r="E110" s="15"/>
-      <c r="F110" s="13"/>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F110" s="15"/>
+      <c r="G110" s="15"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="29"/>
       <c r="B111" s="15"/>
       <c r="C111" s="30"/>
       <c r="D111" s="8"/>
       <c r="E111" s="15"/>
-      <c r="F111" s="13"/>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F111" s="15"/>
+      <c r="G111" s="15"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="29"/>
       <c r="B112" s="15"/>
       <c r="C112" s="30"/>
       <c r="D112" s="8"/>
       <c r="E112" s="15"/>
-      <c r="F112" s="13"/>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F112" s="15"/>
+      <c r="G112" s="15"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="29"/>
       <c r="B113" s="15"/>
       <c r="C113" s="30"/>
       <c r="D113" s="8"/>
       <c r="E113" s="15"/>
-      <c r="F113" s="13"/>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F113" s="15"/>
+      <c r="G113" s="15"/>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="29"/>
       <c r="B114" s="15"/>
       <c r="C114" s="30"/>
       <c r="D114" s="8"/>
       <c r="E114" s="15"/>
-      <c r="F114" s="13"/>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F114" s="15"/>
+      <c r="G114" s="15"/>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="29"/>
       <c r="B115" s="15"/>
       <c r="C115" s="30"/>
       <c r="D115" s="8"/>
       <c r="E115" s="15"/>
-      <c r="F115" s="13"/>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F115" s="15"/>
+      <c r="G115" s="15"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="29"/>
       <c r="B116" s="15"/>
       <c r="C116" s="30"/>
       <c r="D116" s="8"/>
       <c r="E116" s="15"/>
-      <c r="F116" s="13"/>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F116" s="15"/>
+      <c r="G116" s="15"/>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="29"/>
       <c r="B117" s="15"/>
       <c r="C117" s="30"/>
       <c r="D117" s="8"/>
       <c r="E117" s="15"/>
-      <c r="F117" s="13"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F117" s="15"/>
+      <c r="G117" s="15"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="29"/>
       <c r="B118" s="15"/>
       <c r="C118" s="30"/>
       <c r="D118" s="8"/>
       <c r="E118" s="15"/>
-      <c r="F118" s="13"/>
-    </row>
-    <row r="119" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F118" s="15"/>
+      <c r="G118" s="15"/>
+    </row>
+    <row r="119" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="29"/>
       <c r="B119" s="15"/>
       <c r="C119" s="30"/>
@@ -3041,7 +3131,7 @@
       <c r="E119" s="15"/>
       <c r="F119" s="13"/>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="29"/>
       <c r="B120" s="15"/>
       <c r="C120" s="30"/>
@@ -3049,7 +3139,7 @@
       <c r="E120" s="15"/>
       <c r="F120" s="13"/>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="29"/>
       <c r="B121" s="15"/>
       <c r="C121" s="30"/>
@@ -3057,7 +3147,7 @@
       <c r="E121" s="15"/>
       <c r="F121" s="13"/>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="29"/>
       <c r="B122" s="15"/>
       <c r="C122" s="30"/>
@@ -3065,7 +3155,7 @@
       <c r="E122" s="15"/>
       <c r="F122" s="13"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="29"/>
       <c r="B123" s="15"/>
       <c r="C123" s="30"/>
@@ -3073,7 +3163,7 @@
       <c r="E123" s="15"/>
       <c r="F123" s="13"/>
     </row>
-    <row r="124" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="29"/>
       <c r="B124" s="15"/>
       <c r="C124" s="30"/>
@@ -3081,7 +3171,7 @@
       <c r="E124" s="15"/>
       <c r="F124" s="13"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="29"/>
       <c r="B125" s="15"/>
       <c r="C125" s="30"/>
@@ -3089,7 +3179,7 @@
       <c r="E125" s="15"/>
       <c r="F125" s="13"/>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="29"/>
       <c r="B126" s="15"/>
       <c r="C126" s="30"/>
@@ -3097,7 +3187,7 @@
       <c r="E126" s="15"/>
       <c r="F126" s="13"/>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="29"/>
       <c r="B127" s="15"/>
       <c r="C127" s="30"/>
@@ -3105,7 +3195,7 @@
       <c r="E127" s="15"/>
       <c r="F127" s="13"/>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="13"/>
       <c r="B128" s="13"/>
       <c r="C128" s="13"/>
@@ -3122,54 +3212,12 @@
       <c r="F130" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="72">
-    <mergeCell ref="A59:A72"/>
-    <mergeCell ref="E68:E70"/>
-    <mergeCell ref="A73:A95"/>
-    <mergeCell ref="F59:F72"/>
-    <mergeCell ref="G59:G72"/>
-    <mergeCell ref="F73:F95"/>
-    <mergeCell ref="G73:G95"/>
-    <mergeCell ref="E73:E76"/>
-    <mergeCell ref="E77:E80"/>
-    <mergeCell ref="E81:E84"/>
-    <mergeCell ref="E85:E88"/>
-    <mergeCell ref="E89:E92"/>
-    <mergeCell ref="B73:B95"/>
-    <mergeCell ref="F49:F58"/>
-    <mergeCell ref="G49:G58"/>
-    <mergeCell ref="E59:E60"/>
-    <mergeCell ref="E61:E63"/>
-    <mergeCell ref="B59:B72"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="F40:F48"/>
-    <mergeCell ref="G40:G48"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="G24:G26"/>
-    <mergeCell ref="G32:G33"/>
-    <mergeCell ref="F34:F35"/>
-    <mergeCell ref="G34:G35"/>
-    <mergeCell ref="F4:F23"/>
-    <mergeCell ref="G4:G23"/>
-    <mergeCell ref="F24:F26"/>
-    <mergeCell ref="F27:F31"/>
-    <mergeCell ref="G27:G31"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="E38:E39"/>
-    <mergeCell ref="B40:B48"/>
-    <mergeCell ref="A40:A48"/>
-    <mergeCell ref="E40:E48"/>
-    <mergeCell ref="B49:B58"/>
-    <mergeCell ref="A49:A58"/>
-    <mergeCell ref="E49:E58"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:E3"/>
+  <mergeCells count="77">
+    <mergeCell ref="B96:B98"/>
+    <mergeCell ref="A96:A98"/>
+    <mergeCell ref="F96:F98"/>
+    <mergeCell ref="G96:G98"/>
+    <mergeCell ref="E96:E98"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="G2:G3"/>
@@ -3186,14 +3234,61 @@
     <mergeCell ref="E34:E35"/>
     <mergeCell ref="E36:E37"/>
     <mergeCell ref="B27:B31"/>
+    <mergeCell ref="A49:A58"/>
+    <mergeCell ref="E49:E58"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:E3"/>
     <mergeCell ref="A27:A31"/>
     <mergeCell ref="E27:E31"/>
     <mergeCell ref="B32:B33"/>
     <mergeCell ref="A32:A33"/>
     <mergeCell ref="E32:E33"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="B40:B48"/>
+    <mergeCell ref="A40:A48"/>
+    <mergeCell ref="E40:E48"/>
+    <mergeCell ref="F4:F23"/>
+    <mergeCell ref="G4:G23"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="F27:F31"/>
+    <mergeCell ref="G27:G31"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="G24:G26"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="F40:F48"/>
+    <mergeCell ref="G40:G48"/>
+    <mergeCell ref="F49:F58"/>
+    <mergeCell ref="G49:G58"/>
+    <mergeCell ref="E59:E60"/>
+    <mergeCell ref="E61:E63"/>
+    <mergeCell ref="B59:B72"/>
+    <mergeCell ref="B49:B58"/>
     <mergeCell ref="E64:E65"/>
     <mergeCell ref="E66:E67"/>
     <mergeCell ref="E71:E72"/>
+    <mergeCell ref="A59:A72"/>
+    <mergeCell ref="E68:E70"/>
+    <mergeCell ref="A73:A95"/>
+    <mergeCell ref="F59:F72"/>
+    <mergeCell ref="G59:G72"/>
+    <mergeCell ref="F73:F95"/>
+    <mergeCell ref="G73:G95"/>
+    <mergeCell ref="E73:E76"/>
+    <mergeCell ref="E77:E80"/>
+    <mergeCell ref="E81:E84"/>
+    <mergeCell ref="E85:E88"/>
+    <mergeCell ref="E89:E92"/>
+    <mergeCell ref="B73:B95"/>
     <mergeCell ref="E93:E95"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
